--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7472527472527473</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5985915492957746</v>
+        <v>0.6267605633802817</v>
       </c>
       <c r="D2">
-        <v>0.456</v>
+        <v>0.4140625</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
